--- a/tests/fixtures/valid_books.xlsx
+++ b/tests/fixtures/valid_books.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,50 +444,45 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Series</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Series Number</t>
+          <t>Publisher</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>Publication Year</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Publication Year</t>
+          <t>Shelf</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Shelf</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Tags</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Rating</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>Rating</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t>Cover Image</t>
         </is>
@@ -509,10 +504,8 @@
           <t>Frank Herbert</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>9780441013593</t>
-        </is>
+      <c r="D2" t="n">
+        <v>9780441013593</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -521,46 +514,43 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dune</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="inlineStr">
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Ace Books</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="H2" t="n">
         <v>1965</v>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>favorites, classic</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>favorites, classic</t>
+          <t>First edition reprint.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>First edition reprint.</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
           <t>5/5</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -578,10 +568,8 @@
           <t>Ursula K. Le Guin</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>9780441478125</t>
-        </is>
+      <c r="D3" t="n">
+        <v>9780441478125</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -590,46 +578,43 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hainish Cycle</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H3" t="inlineStr">
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Ace Books</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="H3" t="n">
         <v>1969</v>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>On Loan</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>On Loan</t>
+          <t>award-winner</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>award-winner</t>
+          <t>Signed copy.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Signed copy.</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
           <t>4/5</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -647,10 +632,8 @@
           <t>Isaac Asimov</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>9780553293357</t>
-        </is>
+      <c r="D4" t="n">
+        <v>9780553293357</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -659,34 +642,31 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="inlineStr">
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Bantam Spectra</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="H4" t="n">
         <v>1951</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
           <t>classic</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -704,10 +684,8 @@
           <t>J.R.R. Tolkien</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>9780547928227</t>
-        </is>
+      <c r="D5" t="n">
+        <v>9780547928227</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -716,44 +694,43 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Middle-earth</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Houghton Mifflin</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="H5" t="n">
         <v>1937</v>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>favorites, fantasy</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>favorites, fantasy</t>
+          <t>Well loved copy.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Well loved copy.</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
           <t>5/5</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -779,34 +756,31 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mistborn</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
         <v>2006</v>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
           <t>fantasy</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -824,10 +798,8 @@
           <t>William Gibson</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>9780441569595</t>
-        </is>
+      <c r="D7" t="n">
+        <v>9780441569595</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -835,33 +807,32 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Ace Books</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="H7" t="n">
         <v>1984</v>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>On Loan</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>On Loan</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
           <t>cyberpunk, classic</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>3/5</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -879,52 +850,53 @@
           <t>George Orwell</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>9780451524935</t>
-        </is>
+      <c r="D8" t="n">
+        <v>9780451524935</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Dystopian</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Signet Classics</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="H8" t="n">
         <v>1949</v>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>classic, dystopian</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>classic, dystopian</t>
+          <t>Annotated edition.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Annotated edition.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
           <t>5/5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -948,30 +920,33 @@
           <t>Dystopian</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="n">
+      <c r="H9" t="n">
         <v>1932</v>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
           <t>dystopian</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -989,10 +964,8 @@
           <t>Patrick Rothfuss</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>9780756404079</t>
-        </is>
+      <c r="D10" t="n">
+        <v>9780756404079</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1001,38 +974,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kingkiller Chronicle</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>DAW Books</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="H10" t="n">
         <v>2007</v>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
           <t>fantasy, favorites</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>4/5</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1050,44 +1020,45 @@
           <t>Neal Stephenson</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>9780553380958</t>
-        </is>
+      <c r="D11" t="n">
+        <v>9780553380958</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Cyberpunk</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Bantam Books</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="H11" t="n">
         <v>1992</v>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
           <t>cyberpunk</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
